--- a/resources/templates/standard/M4200-01.xlsx
+++ b/resources/templates/standard/M4200-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="127">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>AM 조도 측정 체크시트 (갑지)</t>
   </si>
@@ -970,12 +973,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1010,21 +1015,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -1131,7 +1136,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2237,7 +2242,7 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -2385,7 +2390,7 @@
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -2437,21 +2442,21 @@
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
@@ -2459,25 +2464,25 @@
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R30" s="4"/>
       <c r="S30" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X30" s="12"/>
       <c r="Y30" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z30" s="13"/>
       <c r="AA30" s="13"/>
@@ -2485,25 +2490,25 @@
       <c r="AC30" s="13"/>
       <c r="AD30" s="13"/>
       <c r="AE30" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF30" s="13"/>
       <c r="AG30" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH30" s="4"/>
       <c r="AI30" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="4"/>
       <c r="AL30" s="4"/>
       <c r="AM30" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN30" s="12"/>
       <c r="AO30" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP30" s="13"/>
       <c r="AQ30" s="13"/>
@@ -2511,7 +2516,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
       <c r="AU30" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV30" s="13"/>
     </row>
@@ -2525,15 +2530,15 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L31" s="14"/>
       <c r="M31" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N31" s="14"/>
       <c r="O31" s="13"/>
@@ -2547,15 +2552,15 @@
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
       <c r="Y31" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z31" s="14"/>
       <c r="AA31" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB31" s="14"/>
       <c r="AC31" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD31" s="14"/>
       <c r="AE31" s="13"/>
@@ -2569,15 +2574,15 @@
       <c r="AM31" s="12"/>
       <c r="AN31" s="12"/>
       <c r="AO31" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP31" s="14"/>
       <c r="AQ31" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR31" s="14"/>
       <c r="AS31" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT31" s="14"/>
       <c r="AU31" s="13"/>
@@ -2589,13 +2594,13 @@
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
       <c r="G32" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17">
@@ -2617,13 +2622,13 @@
       </c>
       <c r="R32" s="16"/>
       <c r="S32" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T32" s="16"/>
       <c r="U32" s="16"/>
       <c r="V32" s="16"/>
       <c r="W32" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X32" s="17"/>
       <c r="Y32" s="17">
@@ -2645,13 +2650,13 @@
       </c>
       <c r="AH32" s="16"/>
       <c r="AI32" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ32" s="16"/>
       <c r="AK32" s="16"/>
       <c r="AL32" s="16"/>
       <c r="AM32" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN32" s="17"/>
       <c r="AO32" s="17">
@@ -2675,7 +2680,7 @@
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
@@ -2695,7 +2700,7 @@
       </c>
       <c r="R33" s="16"/>
       <c r="S33" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T33" s="16"/>
       <c r="U33" s="16"/>
@@ -2715,7 +2720,7 @@
       </c>
       <c r="AH33" s="16"/>
       <c r="AI33" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ33" s="16"/>
       <c r="AK33" s="16"/>
@@ -2737,7 +2742,7 @@
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
@@ -2757,7 +2762,7 @@
       </c>
       <c r="R34" s="16"/>
       <c r="S34" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T34" s="16"/>
       <c r="U34" s="16"/>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="AH34" s="16"/>
       <c r="AI34" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ34" s="16"/>
       <c r="AK34" s="16"/>
@@ -2799,7 +2804,7 @@
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
@@ -2819,7 +2824,7 @@
       </c>
       <c r="R35" s="16"/>
       <c r="S35" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T35" s="16"/>
       <c r="U35" s="16"/>
@@ -2839,13 +2844,13 @@
       </c>
       <c r="AH35" s="16"/>
       <c r="AI35" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ35" s="16"/>
       <c r="AK35" s="16"/>
       <c r="AL35" s="16"/>
       <c r="AM35" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN35" s="17"/>
       <c r="AO35" s="17">
@@ -2869,7 +2874,7 @@
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
@@ -2889,7 +2894,7 @@
       </c>
       <c r="R36" s="16"/>
       <c r="S36" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -2909,7 +2914,7 @@
       </c>
       <c r="AH36" s="16"/>
       <c r="AI36" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ36" s="16"/>
       <c r="AK36" s="16"/>
@@ -2931,7 +2936,7 @@
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
@@ -2951,7 +2956,7 @@
       </c>
       <c r="R37" s="16"/>
       <c r="S37" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="AH37" s="16"/>
       <c r="AI37" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AJ37" s="16"/>
       <c r="AK37" s="16"/>
@@ -2993,7 +2998,7 @@
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
@@ -3013,7 +3018,7 @@
       </c>
       <c r="R38" s="16"/>
       <c r="S38" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -3033,7 +3038,7 @@
       </c>
       <c r="AH38" s="16"/>
       <c r="AI38" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AJ38" s="16"/>
       <c r="AK38" s="16"/>
@@ -3055,7 +3060,7 @@
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
@@ -3075,7 +3080,7 @@
       </c>
       <c r="R39" s="16"/>
       <c r="S39" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -3095,7 +3100,7 @@
       </c>
       <c r="AH39" s="16"/>
       <c r="AI39" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AJ39" s="16"/>
       <c r="AK39" s="16"/>
@@ -3117,7 +3122,7 @@
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
@@ -3137,7 +3142,7 @@
       </c>
       <c r="R40" s="16"/>
       <c r="S40" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -3157,7 +3162,7 @@
       </c>
       <c r="AH40" s="16"/>
       <c r="AI40" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AJ40" s="16"/>
       <c r="AK40" s="16"/>
@@ -3179,7 +3184,7 @@
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
@@ -3199,7 +3204,7 @@
       </c>
       <c r="R41" s="16"/>
       <c r="S41" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="AH41" s="16"/>
       <c r="AI41" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AJ41" s="16"/>
       <c r="AK41" s="16"/>
@@ -3241,7 +3246,7 @@
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
@@ -3261,7 +3266,7 @@
       </c>
       <c r="R42" s="16"/>
       <c r="S42" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T42" s="16"/>
       <c r="U42" s="16"/>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="AH42" s="16"/>
       <c r="AI42" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AJ42" s="16"/>
       <c r="AK42" s="16"/>
@@ -3303,7 +3308,7 @@
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
@@ -3323,7 +3328,7 @@
       </c>
       <c r="R43" s="16"/>
       <c r="S43" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T43" s="16"/>
       <c r="U43" s="16"/>
@@ -3343,7 +3348,7 @@
       </c>
       <c r="AH43" s="16"/>
       <c r="AI43" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AJ43" s="16"/>
       <c r="AK43" s="16"/>
@@ -3365,7 +3370,7 @@
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
@@ -3385,7 +3390,7 @@
       </c>
       <c r="R44" s="16"/>
       <c r="S44" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T44" s="16"/>
       <c r="U44" s="16"/>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="AH44" s="16"/>
       <c r="AI44" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AJ44" s="16"/>
       <c r="AK44" s="16"/>
@@ -3427,7 +3432,7 @@
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
@@ -3447,7 +3452,7 @@
       </c>
       <c r="R45" s="16"/>
       <c r="S45" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T45" s="16"/>
       <c r="U45" s="16"/>
@@ -3467,7 +3472,7 @@
       </c>
       <c r="AH45" s="16"/>
       <c r="AI45" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AJ45" s="16"/>
       <c r="AK45" s="16"/>
@@ -3489,7 +3494,7 @@
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
@@ -3509,7 +3514,7 @@
       </c>
       <c r="R46" s="16"/>
       <c r="S46" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T46" s="16"/>
       <c r="U46" s="16"/>
@@ -3529,7 +3534,7 @@
       </c>
       <c r="AH46" s="16"/>
       <c r="AI46" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AJ46" s="16"/>
       <c r="AK46" s="16"/>
@@ -3551,7 +3556,7 @@
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
@@ -3571,7 +3576,7 @@
       </c>
       <c r="R47" s="16"/>
       <c r="S47" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T47" s="16"/>
       <c r="U47" s="16"/>
@@ -3591,7 +3596,7 @@
       </c>
       <c r="AH47" s="16"/>
       <c r="AI47" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AJ47" s="16"/>
       <c r="AK47" s="16"/>
@@ -3613,7 +3618,7 @@
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
@@ -3633,7 +3638,7 @@
       </c>
       <c r="R48" s="16"/>
       <c r="S48" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T48" s="16"/>
       <c r="U48" s="16"/>
@@ -3653,7 +3658,7 @@
       </c>
       <c r="AH48" s="16"/>
       <c r="AI48" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AJ48" s="16"/>
       <c r="AK48" s="16"/>
@@ -3675,7 +3680,7 @@
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
@@ -3695,7 +3700,7 @@
       </c>
       <c r="R49" s="16"/>
       <c r="S49" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T49" s="16"/>
       <c r="U49" s="16"/>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="AH49" s="16"/>
       <c r="AI49" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ49" s="16"/>
       <c r="AK49" s="16"/>
@@ -3737,7 +3742,7 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19"/>
@@ -3757,13 +3762,13 @@
       </c>
       <c r="R50" s="19"/>
       <c r="S50" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T50" s="19"/>
       <c r="U50" s="19"/>
       <c r="V50" s="19"/>
       <c r="W50" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X50" s="16"/>
       <c r="Y50" s="16">
@@ -3785,7 +3790,7 @@
       </c>
       <c r="AH50" s="19"/>
       <c r="AI50" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
@@ -3807,7 +3812,7 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -3955,7 +3960,7 @@
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A54" s="20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -4007,21 +4012,21 @@
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J55" s="13"/>
       <c r="K55" s="13"/>
@@ -4029,25 +4034,25 @@
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
       <c r="O55" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P55" s="13"/>
       <c r="Q55" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R55" s="4"/>
       <c r="S55" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
       <c r="W55" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X55" s="12"/>
       <c r="Y55" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z55" s="13"/>
       <c r="AA55" s="13"/>
@@ -4055,25 +4060,25 @@
       <c r="AC55" s="13"/>
       <c r="AD55" s="13"/>
       <c r="AE55" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF55" s="13"/>
       <c r="AG55" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH55" s="4"/>
       <c r="AI55" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ55" s="4"/>
       <c r="AK55" s="4"/>
       <c r="AL55" s="4"/>
       <c r="AM55" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN55" s="12"/>
       <c r="AO55" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP55" s="13"/>
       <c r="AQ55" s="13"/>
@@ -4081,7 +4086,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
       <c r="AU55" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV55" s="13"/>
     </row>
@@ -4095,15 +4100,15 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J56" s="14"/>
       <c r="K56" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L56" s="14"/>
       <c r="M56" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N56" s="14"/>
       <c r="O56" s="13"/>
@@ -4117,15 +4122,15 @@
       <c r="W56" s="12"/>
       <c r="X56" s="12"/>
       <c r="Y56" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z56" s="14"/>
       <c r="AA56" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB56" s="14"/>
       <c r="AC56" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD56" s="14"/>
       <c r="AE56" s="13"/>
@@ -4139,15 +4144,15 @@
       <c r="AM56" s="12"/>
       <c r="AN56" s="12"/>
       <c r="AO56" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP56" s="14"/>
       <c r="AQ56" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR56" s="14"/>
       <c r="AS56" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT56" s="14"/>
       <c r="AU56" s="13"/>
@@ -4159,13 +4164,13 @@
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
       <c r="G57" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H57" s="16"/>
       <c r="I57" s="16">
@@ -4187,13 +4192,13 @@
       </c>
       <c r="R57" s="16"/>
       <c r="S57" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T57" s="16"/>
       <c r="U57" s="16"/>
       <c r="V57" s="16"/>
       <c r="W57" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X57" s="16"/>
       <c r="Y57" s="16">
@@ -4215,13 +4220,13 @@
       </c>
       <c r="AH57" s="21"/>
       <c r="AI57" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ57" s="21"/>
       <c r="AK57" s="21"/>
       <c r="AL57" s="21"/>
       <c r="AM57" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN57" s="21"/>
       <c r="AO57" s="21">
@@ -4245,7 +4250,7 @@
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
@@ -4265,7 +4270,7 @@
       </c>
       <c r="R58" s="16"/>
       <c r="S58" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T58" s="16"/>
       <c r="U58" s="16"/>
@@ -4285,13 +4290,13 @@
       </c>
       <c r="AH58" s="21"/>
       <c r="AI58" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ58" s="21"/>
       <c r="AK58" s="21"/>
       <c r="AL58" s="21"/>
       <c r="AM58" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN58" s="21"/>
       <c r="AO58" s="21">
@@ -4315,7 +4320,7 @@
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
@@ -4335,7 +4340,7 @@
       </c>
       <c r="R59" s="16"/>
       <c r="S59" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T59" s="16"/>
       <c r="U59" s="16"/>
@@ -4355,7 +4360,7 @@
       </c>
       <c r="AH59" s="21"/>
       <c r="AI59" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ59" s="21"/>
       <c r="AK59" s="21"/>
@@ -4377,7 +4382,7 @@
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
@@ -4397,7 +4402,7 @@
       </c>
       <c r="R60" s="16"/>
       <c r="S60" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T60" s="16"/>
       <c r="U60" s="16"/>
@@ -4417,7 +4422,7 @@
       </c>
       <c r="AH60" s="21"/>
       <c r="AI60" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AJ60" s="21"/>
       <c r="AK60" s="21"/>
@@ -4439,7 +4444,7 @@
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
@@ -4459,13 +4464,13 @@
       </c>
       <c r="R61" s="16"/>
       <c r="S61" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T61" s="16"/>
       <c r="U61" s="16"/>
       <c r="V61" s="16"/>
       <c r="W61" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X61" s="16"/>
       <c r="Y61" s="16">
@@ -4487,7 +4492,7 @@
       </c>
       <c r="AH61" s="21"/>
       <c r="AI61" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AJ61" s="21"/>
       <c r="AK61" s="21"/>
@@ -4509,7 +4514,7 @@
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
@@ -4529,13 +4534,13 @@
       </c>
       <c r="R62" s="21"/>
       <c r="S62" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T62" s="21"/>
       <c r="U62" s="21"/>
       <c r="V62" s="21"/>
       <c r="W62" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X62" s="21"/>
       <c r="Y62" s="21">
@@ -4557,7 +4562,7 @@
       </c>
       <c r="AH62" s="21"/>
       <c r="AI62" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AJ62" s="21"/>
       <c r="AK62" s="21"/>
@@ -4579,7 +4584,7 @@
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
@@ -4599,7 +4604,7 @@
       </c>
       <c r="R63" s="21"/>
       <c r="S63" s="21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T63" s="21"/>
       <c r="U63" s="21"/>
@@ -4619,7 +4624,7 @@
       </c>
       <c r="AH63" s="21"/>
       <c r="AI63" s="21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ63" s="21"/>
       <c r="AK63" s="21"/>
@@ -4641,7 +4646,7 @@
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="R64" s="21"/>
       <c r="S64" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T64" s="21"/>
       <c r="U64" s="21"/>
@@ -4681,7 +4686,7 @@
       </c>
       <c r="AH64" s="21"/>
       <c r="AI64" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ64" s="21"/>
       <c r="AK64" s="21"/>
@@ -4703,7 +4708,7 @@
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
@@ -4723,7 +4728,7 @@
       </c>
       <c r="R65" s="21"/>
       <c r="S65" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T65" s="21"/>
       <c r="U65" s="21"/>
@@ -4743,13 +4748,13 @@
       </c>
       <c r="AH65" s="22"/>
       <c r="AI65" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ65" s="22"/>
       <c r="AK65" s="22"/>
       <c r="AL65" s="22"/>
       <c r="AM65" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN65" s="22"/>
       <c r="AO65" s="22">
@@ -4773,7 +4778,7 @@
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
@@ -4793,7 +4798,7 @@
       </c>
       <c r="R66" s="21"/>
       <c r="S66" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T66" s="21"/>
       <c r="U66" s="21"/>
@@ -4813,7 +4818,7 @@
       </c>
       <c r="AH66" s="22"/>
       <c r="AI66" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AJ66" s="22"/>
       <c r="AK66" s="22"/>
@@ -4835,7 +4840,7 @@
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
@@ -4855,7 +4860,7 @@
       </c>
       <c r="R67" s="21"/>
       <c r="S67" s="21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T67" s="21"/>
       <c r="U67" s="21"/>
@@ -4875,7 +4880,7 @@
       </c>
       <c r="AH67" s="22"/>
       <c r="AI67" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ67" s="22"/>
       <c r="AK67" s="22"/>
@@ -4897,7 +4902,7 @@
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D68" s="16"/>
       <c r="E68" s="16"/>
@@ -4917,7 +4922,7 @@
       </c>
       <c r="R68" s="21"/>
       <c r="S68" s="21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T68" s="21"/>
       <c r="U68" s="21"/>
@@ -4933,7 +4938,7 @@
       <c r="AE68" s="21"/>
       <c r="AF68" s="21"/>
       <c r="AG68" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AH68" s="23"/>
       <c r="AI68" s="24"/>
@@ -4957,7 +4962,7 @@
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
@@ -4977,13 +4982,13 @@
       </c>
       <c r="R69" s="21"/>
       <c r="S69" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T69" s="21"/>
       <c r="U69" s="21"/>
       <c r="V69" s="21"/>
       <c r="W69" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X69" s="21"/>
       <c r="Y69" s="21">
@@ -5023,7 +5028,7 @@
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
@@ -5043,13 +5048,13 @@
       </c>
       <c r="R70" s="21"/>
       <c r="S70" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T70" s="21"/>
       <c r="U70" s="21"/>
       <c r="V70" s="21"/>
       <c r="W70" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X70" s="21"/>
       <c r="Y70" s="21">
@@ -5089,7 +5094,7 @@
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D71" s="16"/>
       <c r="E71" s="16"/>
@@ -5109,7 +5114,7 @@
       </c>
       <c r="R71" s="21"/>
       <c r="S71" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T71" s="21"/>
       <c r="U71" s="21"/>
@@ -5147,13 +5152,13 @@
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D72" s="16"/>
       <c r="E72" s="16"/>
       <c r="F72" s="16"/>
       <c r="G72" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H72" s="16"/>
       <c r="I72" s="16">
@@ -5175,7 +5180,7 @@
       </c>
       <c r="R72" s="21"/>
       <c r="S72" s="21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T72" s="21"/>
       <c r="U72" s="21"/>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D73" s="16"/>
       <c r="E73" s="16"/>
@@ -5233,13 +5238,13 @@
       </c>
       <c r="R73" s="21"/>
       <c r="S73" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T73" s="21"/>
       <c r="U73" s="21"/>
       <c r="V73" s="21"/>
       <c r="W73" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X73" s="21"/>
       <c r="Y73" s="21">
@@ -5279,7 +5284,7 @@
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D74" s="16"/>
       <c r="E74" s="16"/>
@@ -5299,7 +5304,7 @@
       </c>
       <c r="R74" s="21"/>
       <c r="S74" s="21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T74" s="21"/>
       <c r="U74" s="21"/>
@@ -5337,7 +5342,7 @@
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D75" s="19"/>
       <c r="E75" s="19"/>
@@ -5357,7 +5362,7 @@
       </c>
       <c r="R75" s="25"/>
       <c r="S75" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T75" s="25"/>
       <c r="U75" s="25"/>
